--- a/تسعير جرد اخر شهر ٧ سنة ٢٠٢٦.xlsx
+++ b/تسعير جرد اخر شهر ٧ سنة ٢٠٢٦.xlsx
@@ -695,7 +695,7 @@
         <v>1497</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>37533.31</v>
+        <v>37533.38</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>0.0426</v>
@@ -736,7 +736,7 @@
         <v>88.5</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1178.06</v>
+        <v>1178.07</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>-0.1076</v>
@@ -777,7 +777,7 @@
         <v>515</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>14527.57</v>
+        <v>14527.58</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>-0.1877</v>
@@ -818,7 +818,7 @@
         <v>516</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>7973.73</v>
+        <v>7973.75</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0.014</v>
@@ -941,7 +941,7 @@
         <v>145</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>8090.24</v>
+        <v>8090.25</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>-0.0462</v>
@@ -982,7 +982,7 @@
         <v>1462</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>65921.24000000001</v>
+        <v>65921.28999999999</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>0.1286</v>
@@ -1275,7 +1275,7 @@
         <v>1020</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>21842.42</v>
+        <v>21842.38</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>0.0023</v>
@@ -1488,7 +1488,7 @@
         <v>445</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>45375.77</v>
+        <v>45375.76</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>-0.1173</v>
@@ -1911,7 +1911,7 @@
         <v>337.5</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>9051.629999999999</v>
+        <v>9051.610000000001</v>
       </c>
       <c r="L36" s="7" t="n">
         <v>-0.0433</v>
@@ -3277,7 +3277,7 @@
         <v>6.47</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>182.69</v>
+        <v>182.55</v>
       </c>
       <c r="L68" s="7" t="n">
         <v>-0.1939</v>
@@ -4661,7 +4661,7 @@
         <v>754</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>3103.58</v>
+        <v>3103.61</v>
       </c>
       <c r="L100" s="7" t="n">
         <v>-0.1186</v>
@@ -4702,7 +4702,7 @@
         <v>32850</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>15866.75</v>
+        <v>15866.55</v>
       </c>
       <c r="L101" s="7" t="n">
         <v>0.0015</v>
@@ -4743,7 +4743,7 @@
         <v>18300</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>9865.200000000001</v>
+        <v>9865.530000000001</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>-0.1816</v>
@@ -4911,7 +4911,7 @@
         <v>75</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>7658.74</v>
+        <v>7658.75</v>
       </c>
       <c r="L106" s="7" t="n">
         <v>-0.1227</v>
@@ -5327,7 +5327,7 @@
         <v>288.35</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>66872.97</v>
+        <v>66872.98</v>
       </c>
       <c r="L116" s="7" t="n">
         <v>0.4056</v>
@@ -5368,7 +5368,7 @@
         <v>479.15</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>117564.54</v>
+        <v>117564.53</v>
       </c>
       <c r="L117" s="7" t="n">
         <v>0.487</v>
@@ -5676,7 +5676,7 @@
         <v>2450</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>6461.47</v>
+        <v>6461.39</v>
       </c>
       <c r="L125" s="7" t="n"/>
       <c r="M125" s="4" t="inlineStr">
@@ -6689,7 +6689,7 @@
       <c r="I155" s="12" t="n"/>
       <c r="J155" s="12" t="n"/>
       <c r="K155" s="12" t="n">
-        <v>2016665.61</v>
+        <v>2016665.65</v>
       </c>
       <c r="L155" s="12" t="n"/>
       <c r="M155" s="12" t="n"/>
@@ -14173,7 +14173,7 @@
         <v>-0.03</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>11452.27</v>
+        <v>11452.3</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>-0.04</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>41727.51</v>
+        <v>41727.46</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>-0.04</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>22317.18</v>
+        <v>22317.14</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>-0.04</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>21181.18</v>
+        <v>21181.17</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>-0.06</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>10160.53</v>
+        <v>10160.57</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>-0.05</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>6559.94</v>
+        <v>6559.95</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>-0.04</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>17268.7</v>
+        <v>17268.69</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>-0.04</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>11118.47</v>
+        <v>11118.5</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>-0.02</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>16556.6</v>
+        <v>16556.58</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>-0.09</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>4847.55</v>
+        <v>4847.54</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
       <c r="D105" s="12" t="n"/>
       <c r="E105" s="12" t="n"/>
       <c r="F105" s="12" t="n">
-        <v>570329.9399999999</v>
+        <v>570329.9</v>
       </c>
       <c r="G105" s="12" t="n"/>
     </row>
